--- a/product_dashboard/data/code_reader_scanner/202608/summary.xlsx
+++ b/product_dashboard/data/code_reader_scanner/202608/summary.xlsx
@@ -530,7 +530,7 @@
         <v>2664</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008153496301238634</v>
+        <v>0.008163515459810622</v>
       </c>
       <c r="H2" t="n">
         <v>-0.03757225433526012</v>
@@ -542,7 +542,7 @@
         <v>3865370.79</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1082581107072582</v>
+        <v>0.1083071298302218</v>
       </c>
       <c r="L2" t="n">
         <v>-0.007400978896873078</v>
@@ -575,7 +575,7 @@
         <v>13133</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04019514524180442</v>
+        <v>0.0402445377378727</v>
       </c>
       <c r="H3" t="n">
         <v>0.06322862694300513</v>
@@ -587,7 +587,7 @@
         <v>7290720.9</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2041924858463374</v>
+        <v>0.2042849439218254</v>
       </c>
       <c r="L3" t="n">
         <v>0.09338763206293565</v>
@@ -620,7 +620,7 @@
         <v>28190</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08627892670117007</v>
+        <v>0.0863849477522753</v>
       </c>
       <c r="H4" t="n">
         <v>0.1411107512953367</v>
@@ -632,7 +632,7 @@
         <v>6081713.33</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1703316009610938</v>
+        <v>0.1704087268746864</v>
       </c>
       <c r="L4" t="n">
         <v>0.1758116778888281</v>
@@ -665,7 +665,7 @@
         <v>43987</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1346275682442131</v>
+        <v>0.1347930009499586</v>
       </c>
       <c r="H5" t="n">
         <v>0.1045349537967055</v>
@@ -677,7 +677,7 @@
         <v>17237805.02</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4827821975146894</v>
+        <v>0.4830008006267336</v>
       </c>
       <c r="L5" t="n">
         <v>0.09553806551076249</v>
@@ -710,7 +710,7 @@
         <v>21491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06577582170042022</v>
+        <v>0.06585664817822449</v>
       </c>
       <c r="H6" t="n">
         <v>0.169896570495373</v>
@@ -722,7 +722,7 @@
         <v>3743603.12</v>
       </c>
       <c r="K6" t="n">
-        <v>0.104847742435855</v>
+        <v>0.1048952173487769</v>
       </c>
       <c r="L6" t="n">
         <v>0.1443996293977567</v>
@@ -743,37 +743,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.02088300063301</v>
+        <v>30.98759309962242</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005616054885652533</v>
+        <v>0.004536883189568908</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0006579701969051666</v>
+        <v>-0.0004158807561007727</v>
       </c>
       <c r="F7" t="n">
-        <v>112163</v>
+        <v>111762</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3432885156290649</v>
+        <v>0.3424815370943524</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1210806704714691</v>
+        <v>0.1170726344091395</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03865208493457661</v>
+        <v>0.03493874376093853</v>
       </c>
       <c r="J7" t="n">
-        <v>3479395.3</v>
+        <v>3463235.38</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0974480281571419</v>
+        <v>0.09703935387121754</v>
       </c>
       <c r="L7" t="n">
-        <v>0.127376721048081</v>
+        <v>0.1221406624657178</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0393354870514171</v>
+        <v>0.03450833265366526</v>
       </c>
     </row>
     <row r="8">
@@ -788,37 +788,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.04251589926228</v>
+        <v>54.08387428425627</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006629548160947962</v>
+        <v>0.007399915189691963</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05101887820399664</v>
+        <v>0.05182321609754936</v>
       </c>
       <c r="F8" t="n">
-        <v>133654</v>
+        <v>133253</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4090643373294851</v>
+        <v>0.4083381852725768</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1286533411023569</v>
+        <v>0.1252670601845987</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05689591092765234</v>
+        <v>0.05372492270221962</v>
       </c>
       <c r="J8" t="n">
-        <v>7222998.420000001</v>
+        <v>7206838.500000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2022957705929969</v>
+        <v>0.2019345712199945</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1361358027842097</v>
+        <v>0.1335939409957188</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1108175546815722</v>
+        <v>0.1083323370787903</v>
       </c>
     </row>
     <row r="9">
@@ -845,7 +845,7 @@
         <v>75969</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2325123725633625</v>
+        <v>0.2327980878252076</v>
       </c>
       <c r="H9" t="n">
         <v>0.07924308505348687</v>
@@ -857,7 +857,7 @@
         <v>6111994.28</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1711796847842297</v>
+        <v>0.1712571947090057</v>
       </c>
       <c r="L9" t="n">
         <v>0.09042273129466238</v>
@@ -890,7 +890,7 @@
         <v>71048</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2174510530069078</v>
+        <v>0.2177182606563908</v>
       </c>
       <c r="H10" t="n">
         <v>0.1184434229582521</v>
@@ -902,7 +902,7 @@
         <v>5080056.77</v>
       </c>
       <c r="K10" t="n">
-        <v>0.14227803180709</v>
+        <v>0.1423424551033272</v>
       </c>
       <c r="L10" t="n">
         <v>0.1301288243476861</v>
@@ -923,37 +923,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>109.8166516457318</v>
+        <v>109.9026222101605</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.003371276512392996</v>
+        <v>-0.002591060282886692</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05939128888790091</v>
+        <v>0.06022063913389375</v>
       </c>
       <c r="F11" t="n">
-        <v>324658</v>
+        <v>324257</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9936553311439685</v>
+        <v>0.9936475347041338</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1112411777189055</v>
+        <v>0.1098686327261276</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1559671573130523</v>
+        <v>0.1545393692096249</v>
       </c>
       <c r="J11" t="n">
-        <v>35652854.48999999</v>
+        <v>35636694.57</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9985356846990058</v>
+        <v>0.9985350216590609</v>
       </c>
       <c r="L11" t="n">
-        <v>0.107494876436858</v>
+        <v>0.1069928961926494</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2246215366979576</v>
+        <v>0.2240664679286712</v>
       </c>
     </row>
     <row r="12">
@@ -2394,7 +2394,7 @@
         <v>2004</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5012506253126563</v>
+        <v>0.5571309424520434</v>
       </c>
       <c r="H44" t="n">
         <v>0.1029168959823885</v>
@@ -2406,7 +2406,7 @@
         <v>381980.09</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7608246693725818</v>
+        <v>0.7861279181580894</v>
       </c>
       <c r="L44" t="n">
         <v>0.1075605822998824</v>
@@ -2439,7 +2439,7 @@
         <v>2004</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5012506253126563</v>
+        <v>0.5571309424520434</v>
       </c>
       <c r="H45" t="n">
         <v>0.1029168959823885</v>
@@ -2451,7 +2451,7 @@
         <v>381980.09</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7608246693725818</v>
+        <v>0.7861279181580894</v>
       </c>
       <c r="L45" t="n">
         <v>0.1075605822998824</v>
@@ -2480,7 +2480,7 @@
         <v>618</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1545772886443222</v>
+        <v>0.1718098415346122</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>48977.55</v>
       </c>
       <c r="K46" t="n">
-        <v>0.09755306431136002</v>
+        <v>0.1007974510346435</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2521,37 +2521,37 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>40.10514435695539</v>
+        <v>39.88975069252078</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3578695184873343</v>
+        <v>-0.3613182241253725</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.2698113898735615</v>
+        <v>-0.2737330314231765</v>
       </c>
       <c r="F47" t="n">
-        <v>762</v>
+        <v>361</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1905952976488244</v>
+        <v>0.1003614122880178</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.224821973550356</v>
+        <v>-0.6327568667344863</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6281112737920937</v>
+        <v>-0.823816495851635</v>
       </c>
       <c r="J47" t="n">
-        <v>30560.12</v>
+        <v>14400.2</v>
       </c>
       <c r="K47" t="n">
-        <v>0.06086938509016641</v>
+        <v>0.02963609764859765</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5022345606178522</v>
+        <v>-0.7654485034682192</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.7284510878885573</v>
+        <v>-0.8720437405289247</v>
       </c>
     </row>
     <row r="48">
@@ -2566,37 +2566,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>57.63599275362319</v>
+        <v>64.73723186925434</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.0771800383028417</v>
+        <v>0.03651914333009976</v>
       </c>
       <c r="E48" t="n">
-        <v>0.04937025204166412</v>
+        <v>0.178661493929912</v>
       </c>
       <c r="F48" t="n">
-        <v>1380</v>
+        <v>979</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3451725862931466</v>
+        <v>0.27217125382263</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4038657171922686</v>
+        <v>-0.004069175991861629</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3265007320644217</v>
+        <v>-0.522205954123963</v>
       </c>
       <c r="J48" t="n">
-        <v>79537.67</v>
+        <v>63377.75000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1584224494015264</v>
+        <v>0.1304335486832412</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2955153073673229</v>
+        <v>0.03230136451695609</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2932499034565659</v>
+        <v>-0.4368425560969332</v>
       </c>
     </row>
     <row r="49">
@@ -2623,7 +2623,7 @@
         <v>614</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1535767883941971</v>
+        <v>0.1706978037253267</v>
       </c>
       <c r="H49" t="n">
         <v>0.03367003367003374</v>
@@ -2635,7 +2635,7 @@
         <v>40542.84</v>
       </c>
       <c r="K49" t="n">
-        <v>0.08075288122589186</v>
+        <v>0.08343853315866938</v>
       </c>
       <c r="L49" t="n">
         <v>0.1153886997635674</v>
@@ -2687,37 +2687,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>125.5779389694847</v>
+        <v>135.0849819293856</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.03708732335242237</v>
+        <v>0.035811246720034</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3229599720880842</v>
+        <v>0.4231163959956861</v>
       </c>
       <c r="F51" t="n">
-        <v>3998</v>
+        <v>3597</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.17796110783736</v>
+        <v>0.0598114319387153</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.08113077453458972</v>
+        <v>-0.1732934957481039</v>
       </c>
       <c r="J51" t="n">
-        <v>502060.6</v>
+        <v>485900.6800000001</v>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1342736833344182</v>
+        <v>0.09776460060458536</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2156272048743189</v>
+        <v>0.1764995808771508</v>
       </c>
     </row>
     <row r="52">
@@ -14009,17 +14009,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0BY1TS725</t>
+          <t>B00UJV3E12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VDIAGTOOL VD10 OBD2 Scanner Code Reader Car Diagnostic Tool Engine Fault Code Reader for Turn Off CEL with Freeze Frame/I/M Readiness for All OBDII Protocol Cars, OBD2 Scanner Diagnostic Tool</t>
+          <t>FOXWELL NT301 OBD2 Scanner Live Data Professional Mechanic OBDII Diagnostic Code Reader Tool for Check Engine Light</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>vdiagtool</t>
+          <t>foxwell</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -14028,40 +14028,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18.40078437701743</v>
+        <v>64.77930923176243</v>
       </c>
       <c r="F23" t="n">
-        <v>114011.26</v>
+        <v>401372.6</v>
       </c>
       <c r="G23" t="n">
         <v>6196</v>
       </c>
       <c r="H23" t="n">
-        <v>3176</v>
+        <v>30143</v>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B0BY1TS725</t>
+          <t>https://amazon.com/dp/B00UJV3E12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B00UJV3E12</t>
+          <t>B0BY1TS725</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FOXWELL NT301 OBD2 Scanner Live Data Professional Mechanic OBDII Diagnostic Code Reader Tool for Check Engine Light</t>
+          <t>VDIAGTOOL VD10 OBD2 Scanner Code Reader Car Diagnostic Tool Engine Fault Code Reader for Turn Off CEL with Freeze Frame/I/M Readiness for All OBDII Protocol Cars, OBD2 Scanner Diagnostic Tool</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>foxwell</t>
+          <t>vdiagtool</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -14070,23 +14070,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>64.77930923176243</v>
+        <v>18.40078437701743</v>
       </c>
       <c r="F24" t="n">
-        <v>401372.6</v>
+        <v>114011.26</v>
       </c>
       <c r="G24" t="n">
         <v>6196</v>
       </c>
       <c r="H24" t="n">
-        <v>30143</v>
+        <v>3176</v>
       </c>
       <c r="I24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://amazon.com/dp/B00UJV3E12</t>
+          <t>https://amazon.com/dp/B0BY1TS725</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16287,7 @@
         <v>43270</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3857778411775719</v>
+        <v>0.3871620049748573</v>
       </c>
       <c r="H52" t="n">
         <v>0.1208102367507642</v>
@@ -16299,7 +16299,7 @@
         <v>1466660.63</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4215274504739372</v>
+        <v>0.4234943539991209</v>
       </c>
       <c r="L52" t="n">
         <v>0.1662143353225214</v>
@@ -16332,7 +16332,7 @@
         <v>6798</v>
       </c>
       <c r="G53" t="n">
-        <v>0.06060822196267932</v>
+        <v>0.06082568314811832</v>
       </c>
       <c r="H53" t="n">
         <v>0.1042884990253412</v>
@@ -16344,7 +16344,7 @@
         <v>429152.4</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1233410874585018</v>
+        <v>0.123916613487588</v>
       </c>
       <c r="L53" t="n">
         <v>0.1207488560930476</v>
@@ -16377,7 +16377,7 @@
         <v>11562</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1030821215552366</v>
+        <v>0.1034519783110538</v>
       </c>
       <c r="H54" t="n">
         <v>-0.04909943251912163</v>
@@ -16389,7 +16389,7 @@
         <v>254630.33</v>
       </c>
       <c r="K54" t="n">
-        <v>0.07318235154252235</v>
+        <v>0.07352383019371904</v>
       </c>
       <c r="L54" t="n">
         <v>-0.1211683396533108</v>
@@ -16422,7 +16422,7 @@
         <v>5936</v>
       </c>
       <c r="G55" t="n">
-        <v>0.05292297816570527</v>
+        <v>0.05311286483778029</v>
       </c>
       <c r="H55" t="n">
         <v>0.1159992479789433</v>
@@ -16434,7 +16434,7 @@
         <v>229985.76</v>
       </c>
       <c r="K55" t="n">
-        <v>0.06609934778034564</v>
+        <v>0.06640777618759486</v>
       </c>
       <c r="L55" t="n">
         <v>0.144482095260446</v>
@@ -16467,7 +16467,7 @@
         <v>6463</v>
       </c>
       <c r="G56" t="n">
-        <v>0.057621497285201</v>
+        <v>0.05782824215744171</v>
       </c>
       <c r="H56" t="n">
         <v>0.09672492788053622</v>
@@ -16479,7 +16479,7 @@
         <v>123692.97</v>
       </c>
       <c r="K56" t="n">
-        <v>0.03555013424315426</v>
+        <v>0.0357160159295901</v>
       </c>
       <c r="L56" t="n">
         <v>0.08288706570652815</v>
@@ -16500,37 +16500,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>40.10514435695539</v>
+        <v>39.88975069252078</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3578695184873343</v>
+        <v>-0.3613182241253725</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2698113898735615</v>
+        <v>-0.2737330314231765</v>
       </c>
       <c r="F57" t="n">
-        <v>762</v>
+        <v>361</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00679368419175664</v>
+        <v>0.003230078201893309</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.224821973550356</v>
+        <v>-0.6327568667344863</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.6281112737920937</v>
+        <v>-0.823816495851635</v>
       </c>
       <c r="J57" t="n">
-        <v>30560.12</v>
+        <v>14400.2</v>
       </c>
       <c r="K57" t="n">
-        <v>0.008783169880122562</v>
+        <v>0.004158019429796886</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.5022345606178522</v>
+        <v>-0.7654485034682192</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.7284510878885573</v>
+        <v>-0.8720437405289247</v>
       </c>
     </row>
     <row r="58">
@@ -16557,7 +16557,7 @@
         <v>129</v>
       </c>
       <c r="G58" t="n">
-        <v>0.001150111890730455</v>
+        <v>0.001154238471036667</v>
       </c>
       <c r="H58" t="n">
         <v>0.08403361344537807</v>
@@ -16569,7 +16569,7 @@
         <v>8980.25</v>
       </c>
       <c r="K58" t="n">
-        <v>0.00258098009156936</v>
+        <v>0.002593023290262183</v>
       </c>
       <c r="L58" t="n">
         <v>0.07144604202385518</v>
@@ -16602,7 +16602,7 @@
         <v>37243</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3320435437711189</v>
+        <v>0.3332349098978186</v>
       </c>
       <c r="H59" t="n">
         <v>0.2086389303563316</v>
@@ -16614,7 +16614,7 @@
         <v>935732.8400000001</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2689354785298468</v>
+        <v>0.2701903674823281</v>
       </c>
       <c r="L59" t="n">
         <v>0.2135916666361888</v>
@@ -16647,7 +16647,7 @@
         <v>45159</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3378798988432819</v>
+        <v>0.3388966852528649</v>
       </c>
       <c r="H60" t="n">
         <v>0.1243371094236276</v>
@@ -16659,7 +16659,7 @@
         <v>1712611.46</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2371053349891221</v>
+        <v>0.2376369971382042</v>
       </c>
       <c r="L60" t="n">
         <v>0.1791138353052961</v>
@@ -16692,7 +16692,7 @@
         <v>8003</v>
       </c>
       <c r="G61" t="n">
-        <v>0.059878492226196</v>
+        <v>0.06005868535792815</v>
       </c>
       <c r="H61" t="n">
         <v>0.114623955431755</v>
@@ -16704,7 +16704,7 @@
         <v>1551745.71</v>
       </c>
       <c r="K61" t="n">
-        <v>0.214834009336527</v>
+        <v>0.2153157324116532</v>
       </c>
       <c r="L61" t="n">
         <v>0.08989620057657377</v>
@@ -16737,7 +16737,7 @@
         <v>11370</v>
       </c>
       <c r="G62" t="n">
-        <v>0.08507040567435319</v>
+        <v>0.08532640916151982</v>
       </c>
       <c r="H62" t="n">
         <v>0.1760446834919323</v>
@@ -16749,7 +16749,7 @@
         <v>1169675.06</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1619376043003482</v>
+        <v>0.1623007175753973</v>
       </c>
       <c r="L62" t="n">
         <v>0.2504450576059405</v>
@@ -16782,7 +16782,7 @@
         <v>7113</v>
       </c>
       <c r="G63" t="n">
-        <v>0.05321950708545947</v>
+        <v>0.05337966124590066</v>
       </c>
       <c r="H63" t="n">
         <v>0.1364435213292858</v>
@@ -16794,7 +16794,7 @@
         <v>445133.74</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0616272791597814</v>
+        <v>0.0617654662304421</v>
       </c>
       <c r="L63" t="n">
         <v>0.2250794356045664</v>
@@ -16827,7 +16827,7 @@
         <v>11562</v>
       </c>
       <c r="G64" t="n">
-        <v>0.08650695078336601</v>
+        <v>0.08676727728456395</v>
       </c>
       <c r="H64" t="n">
         <v>-0.04925581777814325</v>
@@ -16839,7 +16839,7 @@
         <v>254630.33</v>
       </c>
       <c r="K64" t="n">
-        <v>0.03525271849637204</v>
+        <v>0.03533176579439098</v>
       </c>
       <c r="L64" t="n">
         <v>-0.1218572458943439</v>
@@ -16860,37 +16860,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>57.63599275362319</v>
+        <v>64.73723186925434</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0771800383028417</v>
+        <v>0.03651914333009976</v>
       </c>
       <c r="E65" t="n">
-        <v>0.04937025204166412</v>
+        <v>0.178661493929912</v>
       </c>
       <c r="F65" t="n">
-        <v>1380</v>
+        <v>979</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01032516797102967</v>
+        <v>0.007346926523230247</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4038657171922686</v>
+        <v>-0.004069175991861629</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3265007320644217</v>
+        <v>-0.522205954123963</v>
       </c>
       <c r="J65" t="n">
-        <v>79537.67</v>
+        <v>63377.75</v>
       </c>
       <c r="K65" t="n">
-        <v>0.01101172468482971</v>
+        <v>0.008794112702816916</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2955153073673229</v>
+        <v>0.03230136451695609</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2932499034565659</v>
+        <v>-0.4368425560969332</v>
       </c>
     </row>
     <row r="66">
@@ -16946,7 +16946,7 @@
         <v>49067</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3671195774163137</v>
+        <v>0.3682243551739923</v>
       </c>
       <c r="H67" t="n">
         <v>0.1681784634430874</v>
@@ -16958,7 +16958,7 @@
         <v>2009664.45</v>
       </c>
       <c r="K67" t="n">
-        <v>0.2782313290330195</v>
+        <v>0.2788552081470953</v>
       </c>
       <c r="L67" t="n">
         <v>0.09746713789034112</v>
@@ -17718,7 +17718,7 @@
         <v>21129</v>
       </c>
       <c r="G85" t="n">
-        <v>0.06508079271109907</v>
+        <v>0.06516127639495832</v>
       </c>
       <c r="H85" t="n">
         <v>0.1149279721386733</v>
@@ -17730,7 +17730,7 @@
         <v>5731224.99</v>
       </c>
       <c r="K85" t="n">
-        <v>0.1607508030418016</v>
+        <v>0.1608236975722409</v>
       </c>
       <c r="L85" t="n">
         <v>0.06594433295152791</v>
@@ -17763,7 +17763,7 @@
         <v>14566</v>
       </c>
       <c r="G86" t="n">
-        <v>0.04486567403236637</v>
+        <v>0.04492115821709323</v>
       </c>
       <c r="H86" t="n">
         <v>0.2610163622197212</v>
@@ -17775,7 +17775,7 @@
         <v>3461277.24</v>
       </c>
       <c r="K86" t="n">
-        <v>0.09708275226520299</v>
+        <v>0.09712677569467408</v>
       </c>
       <c r="L86" t="n">
         <v>0.2774188165350049</v>
@@ -17808,7 +17808,7 @@
         <v>50387</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1552002414848856</v>
+        <v>0.1553921734920141</v>
       </c>
       <c r="H87" t="n">
         <v>0.1152254266173833</v>
@@ -17820,7 +17820,7 @@
         <v>3131589.21</v>
       </c>
       <c r="K87" t="n">
-        <v>0.08783558160478724</v>
+        <v>0.08787541178513965</v>
       </c>
       <c r="L87" t="n">
         <v>0.06953017566017849</v>
@@ -17853,7 +17853,7 @@
         <v>17255</v>
       </c>
       <c r="G88" t="n">
-        <v>0.05314823598987242</v>
+        <v>0.05321396299848577</v>
       </c>
       <c r="H88" t="n">
         <v>0.166114752990471</v>
@@ -17865,7 +17865,7 @@
         <v>2489244.04</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0698189268603497</v>
+        <v>0.06985058715562015</v>
       </c>
       <c r="L88" t="n">
         <v>0.2021052347825441</v>
@@ -17898,7 +17898,7 @@
         <v>6667</v>
       </c>
       <c r="G89" t="n">
-        <v>0.02053545577191999</v>
+        <v>0.02056085142340798</v>
       </c>
       <c r="H89" t="n">
         <v>0.1818826449211133</v>
@@ -17910,7 +17910,7 @@
         <v>2291490.29</v>
       </c>
       <c r="K89" t="n">
-        <v>0.06427228121783975</v>
+        <v>0.06430142631491538</v>
       </c>
       <c r="L89" t="n">
         <v>0.08328863182826884</v>
@@ -17931,37 +17931,37 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>125.5779389694847</v>
+        <v>135.0849819293856</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.03708732335242237</v>
+        <v>0.035811246720034</v>
       </c>
       <c r="E90" t="n">
-        <v>0.3229599720880842</v>
+        <v>0.4231163959956861</v>
       </c>
       <c r="F90" t="n">
-        <v>3998</v>
+        <v>3597</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01231449710156534</v>
+        <v>0.01109305273286313</v>
       </c>
       <c r="H90" t="n">
-        <v>0.17796110783736</v>
+        <v>0.0598114319387153</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.08113077453458972</v>
+        <v>-0.1732934957481039</v>
       </c>
       <c r="J90" t="n">
-        <v>502060.6</v>
+        <v>485900.6800000001</v>
       </c>
       <c r="K90" t="n">
-        <v>0.01408191874624848</v>
+        <v>0.01363484144259118</v>
       </c>
       <c r="L90" t="n">
-        <v>0.1342736833344182</v>
+        <v>0.09776460060458536</v>
       </c>
       <c r="M90" t="n">
-        <v>0.2156272048743189</v>
+        <v>0.1764995808771508</v>
       </c>
     </row>
     <row r="91">
@@ -17988,7 +17988,7 @@
         <v>9432</v>
       </c>
       <c r="G91" t="n">
-        <v>0.02905211022060137</v>
+        <v>0.02908803819192801</v>
       </c>
       <c r="H91" t="n">
         <v>0.1299868216125555</v>
@@ -18000,7 +18000,7 @@
         <v>1725977.83</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0484106491524853</v>
+        <v>0.04843260158738118</v>
       </c>
       <c r="L91" t="n">
         <v>0.09075068758463489</v>
@@ -18033,7 +18033,7 @@
         <v>201224</v>
       </c>
       <c r="G92" t="n">
-        <v>0.6198029926876898</v>
+        <v>0.6205694865492496</v>
       </c>
       <c r="H92" t="n">
         <v>0.0918522377045623</v>
@@ -18045,7 +18045,7 @@
         <v>16319990.29</v>
       </c>
       <c r="K92" t="n">
-        <v>0.4577470871112851</v>
+        <v>0.4579546584474375</v>
       </c>
       <c r="L92" t="n">
         <v>0.09039553611151119</v>
